--- a/results/0916-all/江南丘陵山地农林区/tech_selected_summary.xlsx
+++ b/results/0916-all/江南丘陵山地农林区/tech_selected_summary.xlsx
@@ -541,253 +541,253 @@
     <t>资溪县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>技术70</t>
-  </si>
-  <si>
-    <t>技术71</t>
-  </si>
-  <si>
-    <t>技术72</t>
-  </si>
-  <si>
-    <t>技术73</t>
-  </si>
-  <si>
-    <t>技术74</t>
-  </si>
-  <si>
-    <t>技术75</t>
-  </si>
-  <si>
-    <t>技术76</t>
-  </si>
-  <si>
-    <t>技术77</t>
-  </si>
-  <si>
-    <t>技术78</t>
-  </si>
-  <si>
-    <t>技术79</t>
-  </si>
-  <si>
-    <t>技术80</t>
-  </si>
-  <si>
-    <t>技术81</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Tech70</t>
+  </si>
+  <si>
+    <t>Tech71</t>
+  </si>
+  <si>
+    <t>Tech72</t>
+  </si>
+  <si>
+    <t>Tech73</t>
+  </si>
+  <si>
+    <t>Tech74</t>
+  </si>
+  <si>
+    <t>Tech75</t>
+  </si>
+  <si>
+    <t>Tech76</t>
+  </si>
+  <si>
+    <t>Tech77</t>
+  </si>
+  <si>
+    <t>Tech78</t>
+  </si>
+  <si>
+    <t>Tech79</t>
+  </si>
+  <si>
+    <t>Tech80</t>
+  </si>
+  <si>
+    <t>Tech81</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -796,7 +796,7 @@
     <t>4R(Right type)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 59651502.59</t>
+    <t>59651502.59</t>
   </si>
   <si>
     <t>Biochar_sheep &amp; goat</t>
@@ -844,7 +844,7 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 149804369.05</t>
+    <t>149804369.05</t>
   </si>
   <si>
     <t>anaerobic digestion_pig</t>
@@ -859,19 +859,19 @@
     <t>EEF(NI)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 30044715.19</t>
-  </si>
-  <si>
-    <t>总经济成本: 36315903.51</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 25488075.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 4715675.24</t>
+    <t>30044715.19</t>
+  </si>
+  <si>
+    <t>36315903.51</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>25488075.32</t>
+  </si>
+  <si>
+    <t>4715675.24</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -1000,7 +1000,7 @@
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 1267044264.43</t>
+    <t>1267044264.43</t>
   </si>
   <si>
     <t>compost（low）≤30%_wheat</t>
@@ -1012,22 +1012,22 @@
     <t>EEF(NI)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 167693976.35</t>
+    <t>167693976.35</t>
   </si>
   <si>
     <t>nitrification inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 26693.60</t>
+    <t>26693.60</t>
   </si>
   <si>
     <t>Bioflilter_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 362980636.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 20295742.85</t>
+    <t>362980636.50</t>
+  </si>
+  <si>
+    <t>20295742.85</t>
   </si>
   <si>
     <t>By-products source_beef cattle</t>
@@ -1039,16 +1039,16 @@
     <t>4R(Right time)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 240001946.59</t>
+    <t>240001946.59</t>
   </si>
   <si>
     <t>residue rerention_maize</t>
   </si>
   <si>
-    <t>总经济成本: 138992442.26</t>
-  </si>
-  <si>
-    <t>总经济成本: 25012499.00</t>
+    <t>138992442.26</t>
+  </si>
+  <si>
+    <t>25012499.00</t>
   </si>
   <si>
     <t>Zeolite_pig</t>
@@ -1075,7 +1075,7 @@
     <t>4R(Right type)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 423013371.00</t>
+    <t>423013371.00</t>
   </si>
   <si>
     <t>Probiotics_poultry</t>
@@ -1096,7 +1096,7 @@
     <t>cover crop (mix)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 376702448.84</t>
+    <t>376702448.84</t>
   </si>
   <si>
     <t>Cover_poultry</t>
@@ -1108,19 +1108,19 @@
     <t>4R(Right type)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 127610706.45</t>
-  </si>
-  <si>
-    <t>总经济成本: 6306067.04</t>
-  </si>
-  <si>
-    <t>总经济成本: 138270.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 373828568.81</t>
-  </si>
-  <si>
-    <t>总经济成本: 356156941.60</t>
+    <t>127610706.45</t>
+  </si>
+  <si>
+    <t>6306067.04</t>
+  </si>
+  <si>
+    <t>138270.00</t>
+  </si>
+  <si>
+    <t>373828568.81</t>
+  </si>
+  <si>
+    <t>356156941.60</t>
   </si>
   <si>
     <t>Yucca extract_dairy</t>
@@ -1135,16 +1135,16 @@
     <t>Chemical amendments_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 339614721.57</t>
-  </si>
-  <si>
-    <t>总经济成本: 237044747.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 6455227.65</t>
-  </si>
-  <si>
-    <t>总经济成本: 305381834.32</t>
+    <t>339614721.57</t>
+  </si>
+  <si>
+    <t>237044747.25</t>
+  </si>
+  <si>
+    <t>6455227.65</t>
+  </si>
+  <si>
+    <t>305381834.32</t>
   </si>
   <si>
     <t>By-products source_sheep &amp; goat</t>
@@ -1153,19 +1153,19 @@
     <t>manure（high）≥70%_rice</t>
   </si>
   <si>
-    <t>总经济成本: 1206293182.11</t>
+    <t>1206293182.11</t>
   </si>
   <si>
     <t>4R(Right time)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 277634196.80</t>
+    <t>277634196.80</t>
   </si>
   <si>
     <t>4R(Right place)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 545221044.31</t>
+    <t>545221044.31</t>
   </si>
   <si>
     <t>biochar_maize</t>
@@ -1174,46 +1174,46 @@
     <t>irrigation (water-saving irrigation)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 130524801.86</t>
-  </si>
-  <si>
-    <t>总经济成本: 69408095.52</t>
+    <t>130524801.86</t>
+  </si>
+  <si>
+    <t>69408095.52</t>
   </si>
   <si>
     <t>surface crust cover_pig</t>
   </si>
   <si>
-    <t>总经济成本: 549739408.98</t>
-  </si>
-  <si>
-    <t>总经济成本: 8635170.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 817462.73</t>
-  </si>
-  <si>
-    <t>总经济成本: 42767765.62</t>
+    <t>549739408.98</t>
+  </si>
+  <si>
+    <t>8635170.00</t>
+  </si>
+  <si>
+    <t>817462.73</t>
+  </si>
+  <si>
+    <t>42767765.62</t>
   </si>
   <si>
     <t>EEF(CRF)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 271285376.34</t>
-  </si>
-  <si>
-    <t>总经济成本: 134783344.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 26023013.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 140545764.78</t>
-  </si>
-  <si>
-    <t>总经济成本: 1654566.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 16452457.99</t>
+    <t>271285376.34</t>
+  </si>
+  <si>
+    <t>134783344.31</t>
+  </si>
+  <si>
+    <t>26023013.59</t>
+  </si>
+  <si>
+    <t>140545764.78</t>
+  </si>
+  <si>
+    <t>1654566.77</t>
+  </si>
+  <si>
+    <t>16452457.99</t>
   </si>
   <si>
     <t>Low protein diet_dairy</t>
@@ -1228,31 +1228,31 @@
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 373853397.12</t>
-  </si>
-  <si>
-    <t>总经济成本: 140677303.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 297221.93</t>
+    <t>373853397.12</t>
+  </si>
+  <si>
+    <t>140677303.31</t>
+  </si>
+  <si>
+    <t>297221.93</t>
   </si>
   <si>
     <t>compost（mid）30%-70%_friut</t>
   </si>
   <si>
-    <t>总经济成本: 1040090386.67</t>
-  </si>
-  <si>
-    <t>总经济成本: 79410988.36</t>
-  </si>
-  <si>
-    <t>总经济成本: 646474241.23</t>
-  </si>
-  <si>
-    <t>总经济成本: 379983121.67</t>
-  </si>
-  <si>
-    <t>总经济成本: 309229390.09</t>
+    <t>1040090386.67</t>
+  </si>
+  <si>
+    <t>79410988.36</t>
+  </si>
+  <si>
+    <t>646474241.23</t>
+  </si>
+  <si>
+    <t>379983121.67</t>
+  </si>
+  <si>
+    <t>309229390.09</t>
   </si>
   <si>
     <t>Frequent removal_sheep&amp;goat</t>
@@ -1270,19 +1270,19 @@
     <t>irrigation (water-saving irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 444633820.90</t>
-  </si>
-  <si>
-    <t>总经济成本: 924501269.72</t>
-  </si>
-  <si>
-    <t>总经济成本: 212485752.58</t>
-  </si>
-  <si>
-    <t>总经济成本: 174047638.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 237969954.18</t>
+    <t>444633820.90</t>
+  </si>
+  <si>
+    <t>924501269.72</t>
+  </si>
+  <si>
+    <t>212485752.58</t>
+  </si>
+  <si>
+    <t>174047638.50</t>
+  </si>
+  <si>
+    <t>237969954.18</t>
   </si>
   <si>
     <t>Probiotics_pig</t>
@@ -1300,109 +1300,109 @@
     <t>Cover_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 305275104.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 126887657.57</t>
-  </si>
-  <si>
-    <t>总经济成本: 3768588.90</t>
-  </si>
-  <si>
-    <t>总经济成本: 116834.90</t>
-  </si>
-  <si>
-    <t>总经济成本: 416350035.81</t>
-  </si>
-  <si>
-    <t>总经济成本: 28796979.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 136104327.98</t>
-  </si>
-  <si>
-    <t>总经济成本: 230729694.97</t>
-  </si>
-  <si>
-    <t>总经济成本: 1042327370.18</t>
-  </si>
-  <si>
-    <t>总经济成本: 6138571.23</t>
-  </si>
-  <si>
-    <t>总经济成本: 4091099.09</t>
+    <t>305275104.85</t>
+  </si>
+  <si>
+    <t>126887657.57</t>
+  </si>
+  <si>
+    <t>3768588.90</t>
+  </si>
+  <si>
+    <t>116834.90</t>
+  </si>
+  <si>
+    <t>416350035.81</t>
+  </si>
+  <si>
+    <t>28796979.89</t>
+  </si>
+  <si>
+    <t>136104327.98</t>
+  </si>
+  <si>
+    <t>230729694.97</t>
+  </si>
+  <si>
+    <t>1042327370.18</t>
+  </si>
+  <si>
+    <t>6138571.23</t>
+  </si>
+  <si>
+    <t>4091099.09</t>
   </si>
   <si>
     <t>Screw press_pig</t>
   </si>
   <si>
-    <t>总经济成本: 17655300.33</t>
-  </si>
-  <si>
-    <t>总经济成本: 527911750.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 538997291.08</t>
-  </si>
-  <si>
-    <t>总经济成本: 1051729.06</t>
-  </si>
-  <si>
-    <t>总经济成本: 129915415.53</t>
+    <t>17655300.33</t>
+  </si>
+  <si>
+    <t>527911750.10</t>
+  </si>
+  <si>
+    <t>538997291.08</t>
+  </si>
+  <si>
+    <t>1051729.06</t>
+  </si>
+  <si>
+    <t>129915415.53</t>
   </si>
   <si>
     <t>Mixture additives _dairy</t>
   </si>
   <si>
-    <t>总经济成本: 208932396.53</t>
-  </si>
-  <si>
-    <t>总经济成本: 6979208.62</t>
-  </si>
-  <si>
-    <t>总经济成本: 555677228.98</t>
+    <t>208932396.53</t>
+  </si>
+  <si>
+    <t>6979208.62</t>
+  </si>
+  <si>
+    <t>555677228.98</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 104065615.56</t>
-  </si>
-  <si>
-    <t>总经济成本: 582000.92</t>
-  </si>
-  <si>
-    <t>总经济成本: 415754584.57</t>
-  </si>
-  <si>
-    <t>总经济成本: 398265764.71</t>
-  </si>
-  <si>
-    <t>总经济成本: 115143725.27</t>
-  </si>
-  <si>
-    <t>总经济成本: 5189168.69</t>
-  </si>
-  <si>
-    <t>总经济成本: 525325570.22</t>
-  </si>
-  <si>
-    <t>总经济成本: -1172987.20</t>
+    <t>104065615.56</t>
+  </si>
+  <si>
+    <t>582000.92</t>
+  </si>
+  <si>
+    <t>415754584.57</t>
+  </si>
+  <si>
+    <t>398265764.71</t>
+  </si>
+  <si>
+    <t>115143725.27</t>
+  </si>
+  <si>
+    <t>5189168.69</t>
+  </si>
+  <si>
+    <t>525325570.22</t>
+  </si>
+  <si>
+    <t>-1172987.20</t>
   </si>
   <si>
     <t>tillage management (zero tillage)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 441539269.12</t>
-  </si>
-  <si>
-    <t>总经济成本: 378182873.52</t>
-  </si>
-  <si>
-    <t>总经济成本: 1631299.82</t>
-  </si>
-  <si>
-    <t>总经济成本: 167394479.82</t>
+    <t>441539269.12</t>
+  </si>
+  <si>
+    <t>378182873.52</t>
+  </si>
+  <si>
+    <t>1631299.82</t>
+  </si>
+  <si>
+    <t>167394479.82</t>
   </si>
   <si>
     <t>biochar_pig</t>
@@ -1414,109 +1414,109 @@
     <t>tillage management (reduced tillage)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 86426755.36</t>
-  </si>
-  <si>
-    <t>总经济成本: 10507637.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 5228361.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 270331660.18</t>
-  </si>
-  <si>
-    <t>总经济成本: 68116370.11</t>
-  </si>
-  <si>
-    <t>总经济成本: 731177167.86</t>
-  </si>
-  <si>
-    <t>总经济成本: 105742028.88</t>
+    <t>86426755.36</t>
+  </si>
+  <si>
+    <t>10507637.89</t>
+  </si>
+  <si>
+    <t>5228361.15</t>
+  </si>
+  <si>
+    <t>270331660.18</t>
+  </si>
+  <si>
+    <t>68116370.11</t>
+  </si>
+  <si>
+    <t>731177167.86</t>
+  </si>
+  <si>
+    <t>105742028.88</t>
   </si>
   <si>
     <t>compost（mid）30%-70%_maize</t>
   </si>
   <si>
-    <t>总经济成本: 9390513.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 282063583.58</t>
-  </si>
-  <si>
-    <t>总经济成本: 134601555.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 508707546.62</t>
-  </si>
-  <si>
-    <t>总经济成本: 556662723.73</t>
-  </si>
-  <si>
-    <t>总经济成本: 259035319.12</t>
-  </si>
-  <si>
-    <t>总经济成本: 190798682.36</t>
-  </si>
-  <si>
-    <t>总经济成本: 10763224.70</t>
-  </si>
-  <si>
-    <t>总经济成本: 266259344.16</t>
-  </si>
-  <si>
-    <t>总经济成本: 151654419.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 162617371.47</t>
-  </si>
-  <si>
-    <t>总经济成本: 144106401.46</t>
-  </si>
-  <si>
-    <t>总经济成本: 41589777.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 359839625.99</t>
-  </si>
-  <si>
-    <t>总经济成本: 31536841.83</t>
-  </si>
-  <si>
-    <t>总经济成本: 26343708.95</t>
-  </si>
-  <si>
-    <t>总经济成本: 284986.47</t>
-  </si>
-  <si>
-    <t>总经济成本: 77252913.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 62346951.41</t>
+    <t>9390513.20</t>
+  </si>
+  <si>
+    <t>282063583.58</t>
+  </si>
+  <si>
+    <t>134601555.32</t>
+  </si>
+  <si>
+    <t>508707546.62</t>
+  </si>
+  <si>
+    <t>556662723.73</t>
+  </si>
+  <si>
+    <t>259035319.12</t>
+  </si>
+  <si>
+    <t>190798682.36</t>
+  </si>
+  <si>
+    <t>10763224.70</t>
+  </si>
+  <si>
+    <t>266259344.16</t>
+  </si>
+  <si>
+    <t>151654419.15</t>
+  </si>
+  <si>
+    <t>162617371.47</t>
+  </si>
+  <si>
+    <t>144106401.46</t>
+  </si>
+  <si>
+    <t>41589777.00</t>
+  </si>
+  <si>
+    <t>359839625.99</t>
+  </si>
+  <si>
+    <t>31536841.83</t>
+  </si>
+  <si>
+    <t>26343708.95</t>
+  </si>
+  <si>
+    <t>284986.47</t>
+  </si>
+  <si>
+    <t>77252913.20</t>
+  </si>
+  <si>
+    <t>62346951.41</t>
   </si>
   <si>
     <t>Feedstock adjustment_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 39746783.95</t>
-  </si>
-  <si>
-    <t>总经济成本: 2397634.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 184645134.96</t>
-  </si>
-  <si>
-    <t>总经济成本: 119824374.29</t>
-  </si>
-  <si>
-    <t>总经济成本: 181277939.49</t>
-  </si>
-  <si>
-    <t>总经济成本: 1868546.53</t>
-  </si>
-  <si>
-    <t>总经济成本: 5732476.42</t>
+    <t>39746783.95</t>
+  </si>
+  <si>
+    <t>2397634.32</t>
+  </si>
+  <si>
+    <t>184645134.96</t>
+  </si>
+  <si>
+    <t>119824374.29</t>
+  </si>
+  <si>
+    <t>181277939.49</t>
+  </si>
+  <si>
+    <t>1868546.53</t>
+  </si>
+  <si>
+    <t>5732476.42</t>
   </si>
   <si>
     <t>Frequent removal_dairy</t>
@@ -1525,22 +1525,22 @@
     <t>Urease Inhibitor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 889441084.24</t>
-  </si>
-  <si>
-    <t>总经济成本: 157166832.80</t>
-  </si>
-  <si>
-    <t>总经济成本: 57723155.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 4146046.67</t>
+    <t>889441084.24</t>
+  </si>
+  <si>
+    <t>157166832.80</t>
+  </si>
+  <si>
+    <t>57723155.35</t>
+  </si>
+  <si>
+    <t>4146046.67</t>
   </si>
   <si>
     <t>Chemical amendments_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 232387726.75</t>
+    <t>232387726.75</t>
   </si>
 </sst>
 </file>
